--- a/EXCEL/Figur3_overenskomst.xlsx
+++ b/EXCEL/Figur3_overenskomst.xlsx
@@ -70,7 +70,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 7.4.2026 11.08.02</t>
+    <t>Kørsel 7.4.2026 11.20.54</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>

--- a/EXCEL/Figur3_overenskomst.xlsx
+++ b/EXCEL/Figur3_overenskomst.xlsx
@@ -70,7 +70,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 7.4.2026 11.20.54</t>
+    <t>Kørsel 7.4.2026 12.44.38</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>

--- a/EXCEL/Figur3_overenskomst.xlsx
+++ b/EXCEL/Figur3_overenskomst.xlsx
@@ -70,7 +70,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 7.4.2026 12.44.38</t>
+    <t>Kørsel 7.4.2026 12.45.15</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
